--- a/resultsHPC/Quake_10x_Limb_Muscle.xlsx
+++ b/resultsHPC/Quake_10x_Limb_Muscle.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -482,10 +482,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="B2" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -496,7 +496,7 @@
         <v>200</v>
       </c>
       <c r="E2" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="F2" t="n">
         <v>0.001</v>
@@ -507,13 +507,13 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9965912595224199</v>
+        <v>0.9959804895524829</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9907312705702639</v>
+        <v>0.9895274288558731</v>
       </c>
     </row>
     <row r="3">
@@ -521,7 +521,7 @@
         <v>64</v>
       </c>
       <c r="B3" t="n">
-        <v>32</v>
+        <v>512</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E3" t="n">
         <v>800</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005</v>
+        <v>0.0001</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -543,13 +543,13 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>40</v>
+        <v>180</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9953964917218742</v>
+        <v>0.9953976765458731</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9888608661208829</v>
+        <v>0.9885626694179779</v>
       </c>
     </row>
     <row r="4">
@@ -557,7 +557,7 @@
         <v>64</v>
       </c>
       <c r="B4" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
         <v>200</v>
       </c>
       <c r="E4" t="n">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="F4" t="n">
         <v>0.001</v>
@@ -579,13 +579,13 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I4" t="n">
         <v>0.9953812565758478</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9885488639005993</v>
+        <v>0.9885488639005994</v>
       </c>
     </row>
   </sheetData>
